--- a/data/trans_dic/IP2004-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP2004-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores a los que les sangran las encías</t>
+          <t>Menores a los que les sangran las encías (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,45</t>
+          <t>0,0; 8,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,92; 10,84</t>
+          <t>0,94; 11,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,4; 15,85</t>
+          <t>3,24; 16,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,33; 21,13</t>
+          <t>5,15; 19,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,78; 12,43</t>
+          <t>1,78; 12,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,51</t>
+          <t>0,0; 4,01</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,11</t>
+          <t>0,0; 4,18</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,29; 13,57</t>
+          <t>4,35; 13,02</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,07; 10,8</t>
+          <t>3,23; 10,47</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,91</t>
+          <t>0,0; 1,98</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,86; 18,92</t>
+          <t>7,84; 18,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 6,51</t>
+          <t>0,69; 6,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,82</t>
+          <t>0,0; 3,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,78</t>
+          <t>0,0; 1,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,51; 19,73</t>
+          <t>8,58; 19,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,21</t>
+          <t>0,0; 6,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 5,97</t>
+          <t>0,66; 5,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,24</t>
+          <t>0,0; 1,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,47; 16,94</t>
+          <t>9,58; 17,04</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 4,98</t>
+          <t>0,81; 4,94</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,47</t>
+          <t>0,34; 3,39</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,29</t>
+          <t>0,13; 1,41</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,32</t>
+          <t>0,0; 5,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 9,83</t>
+          <t>1,05; 10,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,34; 11,56</t>
+          <t>1,34; 10,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,82</t>
+          <t>0,0; 6,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,96</t>
+          <t>0,0; 3,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,14</t>
+          <t>0,0; 5,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,59</t>
+          <t>0,0; 5,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,32; 12,96</t>
+          <t>1,33; 13,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,02</t>
+          <t>0,0; 3,12</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,82</t>
+          <t>0,72; 5,49</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 5,75</t>
+          <t>0,65; 6,25</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 7,4</t>
+          <t>1,07; 8,12</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,17</t>
+          <t>0,0; 7,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,91; 9,23</t>
+          <t>0,91; 8,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,45; 18,48</t>
+          <t>5,32; 18,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,35</t>
+          <t>0,0; 8,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,2</t>
+          <t>0,0; 4,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,75; 10,33</t>
+          <t>1,75; 10,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,13</t>
+          <t>0,0; 9,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,6</t>
+          <t>0,0; 3,18</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 4,89</t>
+          <t>0,86; 5,32</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,37; 11,8</t>
+          <t>4,25; 12,01</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 7,01</t>
+          <t>0,74; 6,43</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,61; 14,17</t>
+          <t>1,61; 14,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,6; 21,19</t>
+          <t>3,59; 21,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 3,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,47</t>
+          <t>0,0; 8,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,44</t>
+          <t>0,0; 7,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,27; 17,15</t>
+          <t>3,0; 15,59</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,12</t>
+          <t>0,0; 8,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,66</t>
+          <t>0,0; 8,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 7,51</t>
+          <t>0,81; 8,16</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,11; 16,6</t>
+          <t>4,93; 15,78</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,67</t>
+          <t>0,0; 4,4</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,22</t>
+          <t>0,0; 4,7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,71</t>
+          <t>0,0; 5,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,37</t>
+          <t>0,0; 10,17</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,94</t>
+          <t>0,0; 6,47</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,25</t>
+          <t>0,0; 7,4</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,79</t>
+          <t>0,52; 4,8</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,61; 5,69</t>
+          <t>0,62; 5,55</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,18</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 1,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,26; 7,11</t>
+          <t>1,57; 7,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,33</t>
+          <t>0,47; 4,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,21; 7,17</t>
+          <t>1,3; 7,43</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,66</t>
+          <t>0,0; 3,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,78</t>
+          <t>0,0; 4,1</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,87</t>
+          <t>0,0; 2,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,77; 10,07</t>
+          <t>2,76; 9,7</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,72</t>
+          <t>0,0; 1,96</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,69</t>
+          <t>1,06; 4,41</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,35</t>
+          <t>0,27; 2,49</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,52; 7,2</t>
+          <t>2,62; 7,35</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,26; 5,64</t>
+          <t>0,96; 6,01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,71</t>
+          <t>0,42; 4,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,72</t>
+          <t>0,0; 1,77</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0; 1,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,77; 4,57</t>
+          <t>0,9; 5,11</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,14</t>
+          <t>0,38; 3,24</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,28</t>
+          <t>0,0; 4,07</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,41; 4,43</t>
+          <t>1,35; 4,31</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,62</t>
+          <t>0,6; 2,82</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,83</t>
+          <t>0,0; 0,86</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,21</t>
+          <t>0,0; 2,3</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,37; 4,76</t>
+          <t>2,41; 4,73</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,21; 4,4</t>
+          <t>2,1; 4,46</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,87; 4,05</t>
+          <t>1,89; 4,06</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,19</t>
+          <t>0,61; 2,28</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,24; 4,35</t>
+          <t>2,21; 4,33</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,6; 3,72</t>
+          <t>1,55; 3,67</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,5</t>
+          <t>0,94; 2,47</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,54; 3,43</t>
+          <t>1,46; 3,5</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,6; 4,1</t>
+          <t>2,59; 4,15</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2,14; 3,63</t>
+          <t>2,05; 3,59</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,57; 2,94</t>
+          <t>1,61; 2,96</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,18; 2,53</t>
+          <t>1,22; 2,48</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores a los que les sangran las encías (tasa de respuesta: 99,68%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1263</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2246</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4137</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>6585</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2914</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>583</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1263</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>8831</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>7051</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>583</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4167</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>510; 6099</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1802; 9339</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3098; 11649</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1083; 7377</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3088</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4148</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>4985; 14925</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3771; 12210</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2970</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>11768</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2254</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>416</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>14072</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1858</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2167</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>778</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>25840</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>4113</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2824</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>1193</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>7432; 17623</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>658; 6507</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3266</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2255</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>8999; 20751</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 6719</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>703; 5878</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2435</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>19135; 34026</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>1585; 9708</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>698; 6965</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>316; 3524</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2343</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2508</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>718</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>3377</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1203</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2995</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3226</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>3967</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3422</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>651; 6482</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>816; 6548</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3422</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2391</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3904</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3909</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>869; 8704</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4074</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>919; 7063</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>831; 7944</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>1315; 9934</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1399</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2778</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>7399</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1863</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>767</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3536</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1679</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1399</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>3545</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>10935</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>3542</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5335</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>670; 6422</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>3868; 13606</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 6127</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3802</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1361; 7952</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 6808</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4681</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>1305; 8099</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>6403; 18077</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>1068; 9294</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>2078</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>4407</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>566</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>3676</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>543</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>2743</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>8082</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>1109</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>644; 5605</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1502; 8828</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2821</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3352</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1355; 7056</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3738</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3290</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>670; 6740</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>4294; 13747</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3673</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3520</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>732</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1369</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1227</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>1959</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>2159</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3161</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 5202</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3697</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3990</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>572; 5303</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>650; 5833</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>4351</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>4215</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1398</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>1648</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>8355</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>1398</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>5999</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>2711</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>12571</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>2007; 9403</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>608; 5538</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>1601; 9176</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4892</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0; 5350</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3417</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>4267; 15014</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4903</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>2743; 11392</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>710; 6557</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>7287; 20473</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>4133</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>2576</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>3660</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>1934</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>1742</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>7793</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>4511</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>1742</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>1452; 9074</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>665; 6376</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>0; 2630</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>1378; 7862</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>622; 5337</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>0; 6320</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>4102; 13127</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>1940; 9097</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>0; 2639</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>0; 6563</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>22051</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>20955</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>18592</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>7651</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>21548</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>17120</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>11449</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>17057</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>43599</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>38075</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>30040</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>24707</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>15475; 30453</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>13929; 29559</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>12479; 26752</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>3971; 14928</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>15049; 29460</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>10853; 25767</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>6607; 17323</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>10934; 26191</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>34325; 54994</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>28013; 48995</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>21945; 40238</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>17140; 34804</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP2004-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP2004-Provincia-trans_dic.xlsx
@@ -717,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,99</t>
+          <t>0,0; 8,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 11,2</t>
+          <t>0,93; 11,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,24; 16,81</t>
+          <t>3,27; 15,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -742,37 +742,37 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,15; 19,36</t>
+          <t>5,56; 20,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,78; 12,09</t>
+          <t>1,03; 12,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,01</t>
+          <t>0,0; 4,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,18</t>
+          <t>0,0; 4,17</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,35; 13,02</t>
+          <t>4,24; 13,55</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,23; 10,47</t>
+          <t>2,72; 10,27</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,98</t>
+          <t>0,0; 2,03</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,84; 18,59</t>
+          <t>7,7; 19,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 6,78</t>
+          <t>0,68; 6,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,32</t>
+          <t>0,0; 4,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,8</t>
+          <t>0,0; 2,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,58; 19,79</t>
+          <t>8,57; 19,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,68</t>
+          <t>0,0; 6,92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 5,49</t>
+          <t>0,65; 5,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,95</t>
+          <t>0,0; 2,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,58; 17,04</t>
+          <t>9,18; 17,29</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 4,94</t>
+          <t>0,65; 4,66</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,39</t>
+          <t>0,35; 3,43</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,41</t>
+          <t>0,14; 1,31</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,35</t>
+          <t>0,0; 6,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 10,43</t>
+          <t>1,06; 10,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,34; 10,71</t>
+          <t>1,34; 11,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,03</t>
+          <t>0,0; 5,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,59</t>
+          <t>0,0; 3,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,88</t>
+          <t>0,0; 5,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,93</t>
+          <t>0,0; 4,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,33; 13,28</t>
+          <t>1,78; 12,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,12</t>
+          <t>0,0; 3,25</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 5,49</t>
+          <t>0,72; 5,86</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 6,25</t>
+          <t>0,66; 6,06</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 8,12</t>
+          <t>1,05; 7,63</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,55</t>
+          <t>0,0; 7,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,91; 8,73</t>
+          <t>1,12; 9,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,32; 18,7</t>
+          <t>4,83; 16,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,85</t>
+          <t>0,0; 9,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1162,37 +1162,37 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,82</t>
+          <t>0,0; 4,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,75; 10,23</t>
+          <t>1,76; 10,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,03</t>
+          <t>0,0; 10,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,18</t>
+          <t>0,0; 3,46</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 5,32</t>
+          <t>0,86; 5,01</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,25; 12,01</t>
+          <t>4,25; 12,3</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 6,43</t>
+          <t>0,62; 6,08</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,61; 14,05</t>
+          <t>0,0; 12,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,59; 21,09</t>
+          <t>3,51; 20,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1292,47 +1292,47 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,25</t>
+          <t>0,0; 8,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,84</t>
+          <t>0,0; 7,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,0; 15,59</t>
+          <t>2,99; 17,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,78</t>
+          <t>0,0; 8,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,08</t>
+          <t>0,0; 7,4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,81; 8,16</t>
+          <t>0,85; 8,19</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,93; 15,78</t>
+          <t>5,16; 15,7</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,4</t>
+          <t>0,0; 3,28</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,7</t>
+          <t>0,0; 5,17</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,92</t>
+          <t>0,0; 6,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,17</t>
+          <t>0,0; 8,85</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,47</t>
+          <t>0,0; 8,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,4</t>
+          <t>0,0; 7,31</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,8</t>
+          <t>0,52; 5,3</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,62; 5,55</t>
+          <t>0,61; 5,59</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1562,57 +1562,57 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,57; 7,37</t>
+          <t>1,45; 7,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,27</t>
+          <t>0,46; 4,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,3; 7,43</t>
+          <t>1,37; 7,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,87</t>
+          <t>0,0; 3,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,1</t>
+          <t>0,0; 4,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,55</t>
+          <t>0,0; 2,6</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,76; 9,7</t>
+          <t>2,59; 9,32</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,96</t>
+          <t>0,0; 2,0</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,06; 4,41</t>
+          <t>1,06; 4,51</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,49</t>
+          <t>0,27; 2,57</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,62; 7,35</t>
+          <t>2,72; 7,31</t>
         </is>
       </c>
     </row>
@@ -1697,17 +1697,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,96; 6,01</t>
+          <t>0,95; 5,46</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,42; 4,04</t>
+          <t>0,42; 3,92</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,77</t>
+          <t>0,0; 1,79</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1717,12 +1717,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,11</t>
+          <t>1,07; 4,59</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,24</t>
+          <t>0,38; 3,13</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1732,17 +1732,17 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,07</t>
+          <t>0,0; 3,81</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,31</t>
+          <t>1,42; 4,36</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,82</t>
+          <t>0,6; 2,8</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>0,0; 2,0</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,41; 4,73</t>
+          <t>2,34; 4,68</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,46</t>
+          <t>2,2; 4,47</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,06</t>
+          <t>1,91; 4,12</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,28</t>
+          <t>0,61; 2,04</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,21; 4,33</t>
+          <t>2,25; 4,38</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,55; 3,67</t>
+          <t>1,52; 3,65</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,47</t>
+          <t>0,97; 2,57</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,5</t>
+          <t>1,44; 3,44</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,59; 4,15</t>
+          <t>2,64; 4,17</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2,05; 3,59</t>
+          <t>2,07; 3,64</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,96</t>
+          <t>1,66; 2,97</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,22; 2,48</t>
+          <t>1,15; 2,55</t>
         </is>
       </c>
     </row>
@@ -2209,17 +2209,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4167</t>
+          <t>0; 4047</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>510; 6099</t>
+          <t>504; 6026</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1802; 9339</t>
+          <t>1818; 8605</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2234,37 +2234,37 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3098; 11649</t>
+          <t>3344; 12086</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1083; 7377</t>
+          <t>627; 7855</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3088</t>
+          <t>0; 3450</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4148</t>
+          <t>0; 4130</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4985; 14925</t>
+          <t>4864; 15531</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3771; 12210</t>
+          <t>3173; 11969</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 2970</t>
+          <t>0; 3047</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7432; 17623</t>
+          <t>7300; 18140</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>658; 6507</t>
+          <t>649; 6697</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3266</t>
+          <t>0; 3984</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2255</t>
+          <t>0; 2563</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8999; 20751</t>
+          <t>8989; 20245</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 6719</t>
+          <t>0; 6960</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>703; 5878</t>
+          <t>698; 5779</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 2435</t>
+          <t>0; 2519</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19135; 34026</t>
+          <t>18326; 34518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1585; 9708</t>
+          <t>1286; 9163</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>698; 6965</t>
+          <t>710; 7038</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>316; 3524</t>
+          <t>342; 3277</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3422</t>
+          <t>0; 3852</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>651; 6482</t>
+          <t>659; 6762</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>816; 6548</t>
+          <t>817; 7226</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3422</t>
+          <t>0; 3006</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2391</t>
+          <t>0; 2639</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3904</t>
+          <t>0; 3441</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3909</t>
+          <t>0; 2900</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>869; 8704</t>
+          <t>1166; 8329</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4074</t>
+          <t>0; 4240</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>919; 7063</t>
+          <t>920; 7530</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>831; 7944</t>
+          <t>833; 7700</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1315; 9934</t>
+          <t>1291; 9336</t>
         </is>
       </c>
     </row>
@@ -2833,22 +2833,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5335</t>
+          <t>0; 5159</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>670; 6422</t>
+          <t>827; 7043</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3868; 13606</t>
+          <t>3517; 12336</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 6127</t>
+          <t>0; 6567</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2858,37 +2858,37 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3802</t>
+          <t>0; 3847</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1361; 7952</t>
+          <t>1366; 7819</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 6808</t>
+          <t>0; 7679</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4681</t>
+          <t>0; 5080</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1305; 8099</t>
+          <t>1316; 7628</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6403; 18077</t>
+          <t>6395; 18512</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1068; 9294</t>
+          <t>903; 8795</t>
         </is>
       </c>
     </row>
@@ -3041,12 +3041,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>644; 5605</t>
+          <t>0; 4974</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1502; 8828</t>
+          <t>1469; 8437</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -3056,47 +3056,47 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 2821</t>
+          <t>0; 2940</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3352</t>
+          <t>0; 3366</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1355; 7056</t>
+          <t>1352; 7920</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 3738</t>
+          <t>0; 3615</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3290</t>
+          <t>0; 3014</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>670; 6740</t>
+          <t>705; 6766</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4294; 13747</t>
+          <t>4495; 13671</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 3673</t>
+          <t>0; 2740</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 3520</t>
+          <t>0; 3875</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3161</t>
+          <t>0; 3680</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 5202</t>
+          <t>0; 4525</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 3697</t>
+          <t>0; 4877</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 3990</t>
+          <t>0; 3943</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>572; 5303</t>
+          <t>572; 5854</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>650; 5833</t>
+          <t>636; 5873</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -3462,57 +3462,57 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2007; 9403</t>
+          <t>1843; 9359</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>608; 5538</t>
+          <t>597; 5636</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1601; 9176</t>
+          <t>1692; 9485</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 4892</t>
+          <t>0; 4263</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 5350</t>
+          <t>0; 5707</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 3417</t>
+          <t>0; 3484</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>4267; 15014</t>
+          <t>4018; 14435</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 4903</t>
+          <t>0; 4980</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2743; 11392</t>
+          <t>2741; 11634</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>710; 6557</t>
+          <t>712; 6777</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>7287; 20473</t>
+          <t>7584; 20341</t>
         </is>
       </c>
     </row>
@@ -3665,17 +3665,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1452; 9074</t>
+          <t>1435; 8238</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>665; 6376</t>
+          <t>654; 6178</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 2630</t>
+          <t>0; 2667</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3685,12 +3685,12 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1378; 7862</t>
+          <t>1642; 7058</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>622; 5337</t>
+          <t>624; 5160</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -3700,27 +3700,27 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 6320</t>
+          <t>0; 5906</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>4102; 13127</t>
+          <t>4328; 13286</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1940; 9097</t>
+          <t>1926; 9021</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0; 2639</t>
+          <t>0; 2633</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0; 6563</t>
+          <t>0; 5713</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>15475; 30453</t>
+          <t>15021; 30106</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>13929; 29559</t>
+          <t>14564; 29592</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>12479; 26752</t>
+          <t>12574; 27149</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3971; 14928</t>
+          <t>4007; 13380</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>15049; 29460</t>
+          <t>15282; 29798</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10853; 25767</t>
+          <t>10646; 25644</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6607; 17323</t>
+          <t>6782; 17999</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>10934; 26191</t>
+          <t>10765; 25750</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>34325; 54994</t>
+          <t>34895; 55184</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>28013; 48995</t>
+          <t>28308; 49648</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>21945; 40238</t>
+          <t>22538; 40371</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>17140; 34804</t>
+          <t>16155; 35730</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP2004-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP2004-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10,95%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4,78%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>2,72%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>4,13%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>7,44%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10,95%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,78%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,93; 11,07</t>
+          <t>5,33; 21,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,27; 15,49</t>
+          <t>1,78; 12,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 3,59</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 9,45</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,92; 10,84</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>3,4; 15,85</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>5,56; 20,09</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1,03; 12,88</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,48</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,17</t>
+          <t>0,0; 4,11</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,24; 13,55</t>
+          <t>4,29; 13,57</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,72; 10,27</t>
+          <t>3,07; 10,8</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,03</t>
+          <t>0,0; 1,94</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>13,42%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1,85%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>12,41%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>2,35%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>0,67%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>13,42%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,85%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2,02%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,7; 19,13</t>
+          <t>8,51; 19,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 6,98</t>
+          <t>0,0; 7,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,05</t>
+          <t>0,65; 5,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,04</t>
+          <t>0,0; 1,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,57; 19,31</t>
+          <t>7,86; 18,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,92</t>
+          <t>0,69; 6,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 5,4</t>
+          <t>0,0; 2,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,02</t>
+          <t>0,0; 1,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,18; 17,29</t>
+          <t>9,47; 16,94</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 4,66</t>
+          <t>0,67; 4,98</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,43</t>
+          <t>0,35; 3,47</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,31</t>
+          <t>0,13; 1,22</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4,03%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>1,06%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>3,77%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>4,1%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,02</t>
+          <t>0,0; 3,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 10,88</t>
+          <t>0,0; 5,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,34; 11,82</t>
+          <t>0,0; 7,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,29</t>
+          <t>1,07; 9,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,96</t>
+          <t>0,0; 5,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,18</t>
+          <t>1,05; 9,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,4</t>
+          <t>1,34; 11,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,78; 12,7</t>
+          <t>0,0; 5,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,25</t>
+          <t>0,0; 3,02</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 5,86</t>
+          <t>0,6; 5,82</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 6,06</t>
+          <t>0,65; 5,75</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 7,63</t>
+          <t>0,93; 5,37</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4,55%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>1,98%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>3,78%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>10,17%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,12; 9,58</t>
+          <t>0,0; 6,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,83; 16,95</t>
+          <t>1,75; 10,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,48</t>
+          <t>0,0; 8,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 7,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,88</t>
+          <t>0,91; 9,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,76; 10,05</t>
+          <t>5,45; 18,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,19</t>
+          <t>0,0; 9,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,46</t>
+          <t>0,0; 3,6</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 5,01</t>
+          <t>0,86; 4,89</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,25; 12,3</t>
+          <t>4,37; 11,8</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,62; 6,08</t>
+          <t>0,72; 7,05</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>8,12%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>5,21%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>10,53%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>8,12%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,46</t>
+          <t>0,0; 8,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,51; 20,16</t>
+          <t>2,27; 17,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>0,0; 8,12</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 7,25</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,61; 14,17</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3,6; 21,19</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 8,6</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,88</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,99; 17,51</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 8,49</t>
-        </is>
-      </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,4</t>
+          <t>0,0; 8,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,85; 8,19</t>
+          <t>0,86; 7,51</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,16; 15,7</t>
+          <t>5,11; 16,6</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,28</t>
+          <t>0,0; 3,67</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,17</t>
+          <t>0,0; 5,59</t>
         </is>
       </c>
     </row>
@@ -1349,37 +1349,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>1,37%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>2,68%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,89</t>
+          <t>0,0; 6,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,85</t>
+          <t>0,0; 7,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,54</t>
+          <t>0,0; 8,71</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,31</t>
+          <t>0,0; 8,37</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,52; 5,3</t>
+          <t>0,51; 4,79</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,61; 5,59</t>
+          <t>0,61; 5,69</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1,26%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6,02%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>3,41%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>1,54%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3,41%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>0,0; 3,66</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 4,78</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 2,87</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>3,19; 11,04</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>1,45; 7,34</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0,46; 4,34</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1,37; 7,68</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,37</t>
-        </is>
-      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,37</t>
+          <t>1,26; 7,11</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,6</t>
+          <t>0,46; 4,33</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,59; 9,32</t>
+          <t>1,22; 7,87</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,0</t>
+          <t>0,0; 1,72</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,06; 4,51</t>
+          <t>1,02; 4,69</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,57</t>
+          <t>0,27; 2,35</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,72; 7,31</t>
+          <t>2,81; 7,89</t>
         </is>
       </c>
     </row>
@@ -1629,44 +1629,44 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>2,38%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>2,74%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>1,63%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>0,35%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>2,38%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
           <t>2,56%</t>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,95; 5,46</t>
+          <t>0,77; 4,57</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,92</t>
+          <t>0,38; 3,14</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
+          <t>0,0; 4,0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,26; 5,64</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,4; 3,71</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 1,72</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>1,07; 4,59</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,38; 3,13</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,81</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,42; 4,36</t>
+          <t>1,41; 4,43</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,8</t>
+          <t>0,59; 2,62</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,86</t>
+          <t>0,0; 0,83</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,0</t>
+          <t>0,0; 2,08</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>3,17%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>3,43%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>3,16%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>2,82%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,34; 4,68</t>
+          <t>2,24; 4,35</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,2; 4,47</t>
+          <t>1,6; 3,72</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,12</t>
+          <t>1,0; 2,5</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,04</t>
+          <t>1,51; 3,35</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,25; 4,38</t>
+          <t>2,37; 4,76</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,65</t>
+          <t>2,21; 4,4</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,57</t>
+          <t>1,87; 4,05</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,44</t>
+          <t>0,65; 2,35</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,64; 4,17</t>
+          <t>2,6; 4,1</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2,07; 3,64</t>
+          <t>2,14; 3,63</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,97</t>
+          <t>1,57; 2,94</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,55</t>
+          <t>1,22; 2,6</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,44 +2141,44 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6585</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2914</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>462</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>1263</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>2246</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>4137</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>6585</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>2914</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>583</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
           <t>1263</t>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>462</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4047</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>504; 6026</t>
+          <t>3207; 12712</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1818; 8605</t>
+          <t>1086; 7582</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>0; 2233</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4380</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>502; 5900</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1887; 8806</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3344; 12086</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>627; 7855</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3450</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4130</t>
+          <t>0; 4073</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4864; 15531</t>
+          <t>4922; 15550</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3173; 11969</t>
+          <t>3582; 12587</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 3047</t>
+          <t>0; 2299</t>
         </is>
       </c>
     </row>
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>14072</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1858</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2167</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>586</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>11768</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2254</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>657</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>14072</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1858</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2167</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>359</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1193</t>
+          <t>945</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7300; 18140</t>
+          <t>8926; 20685</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>649; 6697</t>
+          <t>0; 7262</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3984</t>
+          <t>697; 6393</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2563</t>
+          <t>0; 2150</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8989; 20245</t>
+          <t>7448; 17937</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 6960</t>
+          <t>658; 6251</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>698; 5779</t>
+          <t>0; 2769</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 2519</t>
+          <t>0; 1924</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18326; 34518</t>
+          <t>18912; 33832</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1286; 9163</t>
+          <t>1313; 9800</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>710; 7038</t>
+          <t>720; 7126</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>342; 3277</t>
+          <t>284; 2601</t>
         </is>
       </c>
     </row>
@@ -2494,37 +2494,37 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,42 +2557,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>718</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2338</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>678</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>2343</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>2508</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>590</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>525</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>651</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>718</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3377</t>
+          <t>592</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3967</t>
+          <t>2930</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3852</t>
+          <t>0; 2639</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>659; 6762</t>
+          <t>0; 3416</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>817; 7226</t>
+          <t>0; 5002</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3006</t>
+          <t>619; 5519</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2639</t>
+          <t>0; 3403</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3441</t>
+          <t>652; 6106</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2900</t>
+          <t>819; 7067</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1166; 8329</t>
+          <t>0; 2998</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4240</t>
+          <t>0; 3947</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>920; 7530</t>
+          <t>773; 7484</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>833; 7700</t>
+          <t>828; 7306</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1291; 9336</t>
+          <t>1058; 6079</t>
         </is>
       </c>
     </row>
@@ -2697,37 +2697,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>767</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3536</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1552</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>1399</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2778</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>7399</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1863</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>767</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3536</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1679</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3542</t>
+          <t>3579</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5159</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>827; 7043</t>
+          <t>0; 4888</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3517; 12336</t>
+          <t>1358; 8033</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 6567</t>
+          <t>0; 5918</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 5067</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3847</t>
+          <t>669; 6790</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1366; 7819</t>
+          <t>3963; 13447</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 7679</t>
+          <t>0; 6342</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 5080</t>
+          <t>0; 5292</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1316; 7628</t>
+          <t>1310; 7456</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6395; 18512</t>
+          <t>6582; 17766</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>903; 8795</t>
+          <t>1007; 9868</t>
         </is>
       </c>
     </row>
@@ -2905,37 +2905,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2973,62 +2973,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3676</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>586</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>2078</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>4407</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>566</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>3676</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>2743</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>8082</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>610</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>543</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>2743</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>8082</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>610</t>
-        </is>
-      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1109</t>
+          <t>1195</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4974</t>
+          <t>0; 3607</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1469; 8437</t>
+          <t>1025; 7757</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>0; 3456</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2871</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>641; 5654</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1509; 8867</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>0; 2940</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>0; 3366</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1352; 7920</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>0; 3615</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3014</t>
+          <t>0; 3130</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>705; 6766</t>
+          <t>710; 6205</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4495; 13671</t>
+          <t>4447; 14455</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 2740</t>
+          <t>0; 3062</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 3875</t>
+          <t>0; 4188</t>
         </is>
       </c>
     </row>
@@ -3113,37 +3113,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -3181,37 +3181,37 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1227</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>732</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>1369</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>1227</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>790</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3680</t>
+          <t>0; 3964</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4525</t>
+          <t>0; 3912</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 4877</t>
+          <t>0; 4652</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 3943</t>
+          <t>0; 4278</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>572; 5854</t>
+          <t>569; 5289</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>636; 5873</t>
+          <t>637; 5977</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,49 +3389,49 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1398</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>1648</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>8456</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>4351</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>1998</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>4215</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>4368</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>1398</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>1648</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>8355</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>1398</t>
-        </is>
-      </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
           <t>5999</t>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>12571</t>
+          <t>12825</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>0; 4622</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0; 6239</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3839</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>4475; 15497</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>1843; 9359</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>597; 5636</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>1692; 9485</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>0; 4263</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 5707</t>
+          <t>1612; 9064</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 3484</t>
+          <t>603; 5622</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>4018; 14435</t>
+          <t>1475; 9542</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 4980</t>
+          <t>0; 4292</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2741; 11634</t>
+          <t>2622; 12115</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>712; 6777</t>
+          <t>710; 6190</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>7584; 20341</t>
+          <t>7340; 20632</t>
         </is>
       </c>
     </row>
@@ -3534,37 +3534,37 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,44 +3597,44 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>3660</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>1934</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>1646</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>4133</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>2576</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>524</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>3660</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>1934</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>1742</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
           <t>7793</t>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1742</t>
+          <t>1646</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1435; 8238</t>
+          <t>1186; 7036</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>654; 6178</t>
+          <t>626; 5166</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 2667</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
+          <t>0; 6326</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>1906; 8506</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>636; 5846</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>0; 2558</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>1642; 7058</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>624; 5160</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>0; 5906</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>4328; 13286</t>
+          <t>4305; 13514</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1926; 9021</t>
+          <t>1916; 8460</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0; 2633</t>
+          <t>0; 2540</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0; 5713</t>
+          <t>0; 6185</t>
         </is>
       </c>
     </row>
@@ -3742,37 +3742,37 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>21548</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>17120</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>11449</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>15627</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>22051</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>20955</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>18592</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>7651</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>21548</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>17120</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>11449</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>17057</t>
+          <t>7955</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>24707</t>
+          <t>23583</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>15021; 30106</t>
+          <t>15280; 29635</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>14564; 29592</t>
+          <t>11243; 26097</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>12574; 27149</t>
+          <t>6984; 17556</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4007; 13380</t>
+          <t>10377; 23077</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>15282; 29798</t>
+          <t>15223; 30597</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10646; 25644</t>
+          <t>14641; 29159</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6782; 17999</t>
+          <t>12341; 26686</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>10765; 25750</t>
+          <t>4007; 14589</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>34895; 55184</t>
+          <t>34429; 54328</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>28308; 49648</t>
+          <t>29207; 49547</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>22538; 40371</t>
+          <t>21326; 39957</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>16155; 35730</t>
+          <t>15940; 34073</t>
         </is>
       </c>
     </row>
